--- a/BaoCao_Whitebox.xlsx
+++ b/BaoCao_Whitebox.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="B1_CFG_va_Basis_Path" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="B2_Coverage_Levels" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="B3_Truoc_va_Sau" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="B4_Coverage_Per_Class" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="B5_Danh_Sach_Test_Whitebox" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B1_CFG_va_Basis_Path" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B2_Coverage_Levels" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B3_Truoc_va_Sau" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B4_Coverage_Per_Class" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B5_Danh_Sach_Test_Whitebox" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -643,6 +643,14 @@
           <t>BẢNG B1 - ĐỒ THỊ LUỒNG ĐIỀU KHIỂN (CFG) VÀ ĐỘ PHỨC TẠP CYCLOMATIC</t>
         </is>
       </c>
+      <c r="B1" s="19" t="n"/>
+      <c r="C1" s="19" t="n"/>
+      <c r="D1" s="19" t="n"/>
+      <c r="E1" s="19" t="n"/>
+      <c r="F1" s="19" t="n"/>
+      <c r="G1" s="19" t="n"/>
+      <c r="H1" s="19" t="n"/>
+      <c r="I1" s="20" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -651,12 +659,21 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>A - BẢNG CHỈ SỐ CFG (Control Flow Graph Metrics)</t>
         </is>
       </c>
+      <c r="B4" s="19" t="n"/>
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="19" t="n"/>
+      <c r="E4" s="19" t="n"/>
+      <c r="F4" s="19" t="n"/>
+      <c r="G4" s="19" t="n"/>
+      <c r="H4" s="19" t="n"/>
+      <c r="I4" s="20" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -771,12 +788,21 @@
         <v>7</v>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>B - DANH SÁCH ĐƯỜNG CƠ SỞ (BASIS PATHS)</t>
         </is>
       </c>
+      <c r="B9" s="19" t="n"/>
+      <c r="C9" s="19" t="n"/>
+      <c r="D9" s="19" t="n"/>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="19" t="n"/>
+      <c r="G9" s="19" t="n"/>
+      <c r="H9" s="19" t="n"/>
+      <c r="I9" s="20" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -853,7 +879,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>calculatePercent_totalZero</t>
+          <t>calculatePercent_whenTotalZero_returnsZero</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
@@ -900,7 +926,7 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>calculatePercent_normalCase</t>
+          <t>calculatePercent_roundsToTwoDecimals</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
@@ -947,7 +973,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>isNodeLocked_tier1Null</t>
+          <t>isNodeLocked_whenTierIsNull_treatsNodeAsTierOne</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -994,7 +1020,7 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>isNodeLocked_explicitTier1</t>
+          <t>isNodeLocked_whenTierOne_alwaysUnlocked</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
@@ -1041,7 +1067,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>isNodeLocked_tier2AllDone</t>
+          <t>isNodeLocked_whenAllLowerTiersDone_returnsUnlocked</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -1088,7 +1114,7 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>isNodeLocked_tier2NotDone</t>
+          <t>isNodeLocked_whenLowerTierNotAllDone_returnsLocked</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
@@ -1107,7 +1133,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t>isNodeLocked()</t>
@@ -1135,7 +1161,8 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>isNodeLocked_tier3Tier1NotDone</t>
+          <t>lockExpression_coversConditionCombinations
+[tier 3 bị khóa khi tier 1 chưa xong]</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
@@ -1154,7 +1181,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>isNodeLocked()</t>
@@ -1182,7 +1209,8 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>isNodeLocked_tier3Tier2NotDone</t>
+          <t>lockExpression_coversConditionCombinations
+[tier 3 bị khóa khi tier 2 chưa xong]</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
@@ -1201,7 +1229,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
           <t>isNodeLocked()</t>
@@ -1229,7 +1257,8 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>isNodeLocked_tier3AllDone</t>
+          <t>lockExpression_coversConditionCombinations
+[tier 3 mở khi tier 1 và tier 2 đã xong]</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
@@ -1288,6 +1317,15 @@
           <t>BẢNG B2 - SO SÁNH CÁC MỨC BAO PHỦ (COVERAGE LEVELS)</t>
         </is>
       </c>
+      <c r="B1" s="19" t="n"/>
+      <c r="C1" s="19" t="n"/>
+      <c r="D1" s="19" t="n"/>
+      <c r="E1" s="19" t="n"/>
+      <c r="F1" s="19" t="n"/>
+      <c r="G1" s="19" t="n"/>
+      <c r="H1" s="19" t="n"/>
+      <c r="I1" s="19" t="n"/>
+      <c r="J1" s="20" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1302,6 +1340,15 @@
           <t>A - BẢNG SO SÁNH 4 MỨC BAO PHỦ</t>
         </is>
       </c>
+      <c r="B4" s="19" t="n"/>
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="19" t="n"/>
+      <c r="E4" s="19" t="n"/>
+      <c r="F4" s="19" t="n"/>
+      <c r="G4" s="19" t="n"/>
+      <c r="H4" s="19" t="n"/>
+      <c r="I4" s="19" t="n"/>
+      <c r="J4" s="20" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1569,6 +1616,17 @@
           <t>B - MA TRẬN TỔ HỢP ĐIỀU KIỆN (MC/DC) cho isNodeLocked()</t>
         </is>
       </c>
+      <c r="B11" s="19" t="n"/>
+      <c r="C11" s="19" t="n"/>
+      <c r="D11" s="19" t="n"/>
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="19" t="n"/>
+      <c r="G11" s="19" t="n"/>
+      <c r="H11" s="19" t="n"/>
+      <c r="I11" s="19" t="n"/>
+      <c r="J11" s="19" t="n"/>
+      <c r="K11" s="19" t="n"/>
+      <c r="L11" s="20" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -2086,6 +2144,11 @@
           <t>BẢNG B3 - ĐỘ BAO PHỦ TRƯỚC VÀ SAU KHI BỔ SUNG TEST</t>
         </is>
       </c>
+      <c r="B1" s="19" t="n"/>
+      <c r="C1" s="19" t="n"/>
+      <c r="D1" s="19" t="n"/>
+      <c r="E1" s="19" t="n"/>
+      <c r="F1" s="20" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2100,6 +2163,11 @@
           <t>A - BẢNG SO SÁNH CHỈ SỐ BAO PHỦ (JaCoCo)</t>
         </is>
       </c>
+      <c r="B4" s="19" t="n"/>
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="19" t="n"/>
+      <c r="E4" s="19" t="n"/>
+      <c r="F4" s="20" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -2299,6 +2367,11 @@
           <t>B - KẾT QUẢ CHẠY TEST SUITE</t>
         </is>
       </c>
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="20" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -2498,6 +2571,11 @@
           <t>C - NHẬN XÉT VÀ KẾT LUẬN</t>
         </is>
       </c>
+      <c r="B20" s="19" t="n"/>
+      <c r="C20" s="19" t="n"/>
+      <c r="D20" s="19" t="n"/>
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="20" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -2526,6 +2604,10 @@
           <t>Đây là mức tăng lớn nhất, cho thấy việc bổ sung test white-box đã bao phủ được nhiều nhánh if/else bị bỏ sót.</t>
         </is>
       </c>
+      <c r="C22" s="19" t="n"/>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="20" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -2538,6 +2620,10 @@
           <t>Toàn bộ bộ test ổn định, không có regression (lỗi hồi quy).</t>
         </is>
       </c>
+      <c r="C23" s="19" t="n"/>
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="19" t="n"/>
+      <c r="F23" s="20" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2550,6 +2636,10 @@
           <t>JaCoCo check sẽ fail build nếu branch &lt; 65%. Project vượt ngưỡng này, đảm bảo CI/CD hoạt động trơn tru.</t>
         </is>
       </c>
+      <c r="C24" s="19" t="n"/>
+      <c r="D24" s="19" t="n"/>
+      <c r="E24" s="19" t="n"/>
+      <c r="F24" s="20" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -2562,6 +2652,10 @@
           <t>File mới thêm đã được test đầy đủ 16/16 nhánh, 158/158 instruction.</t>
         </is>
       </c>
+      <c r="C25" s="19" t="n"/>
+      <c r="D25" s="19" t="n"/>
+      <c r="E25" s="19" t="n"/>
+      <c r="F25" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -2606,6 +2700,14 @@
           <t>BẢNG B4 - ĐỘ BAO PHỦ TỪNG CLASS (JaCoCo - Chi tiết)</t>
         </is>
       </c>
+      <c r="B1" s="19" t="n"/>
+      <c r="C1" s="19" t="n"/>
+      <c r="D1" s="19" t="n"/>
+      <c r="E1" s="19" t="n"/>
+      <c r="F1" s="19" t="n"/>
+      <c r="G1" s="19" t="n"/>
+      <c r="H1" s="19" t="n"/>
+      <c r="I1" s="20" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2620,6 +2722,14 @@
           <t>CHI TIẾT ĐỘ BAO PHỦ TỪNG CLASS (WHITE-BOX)</t>
         </is>
       </c>
+      <c r="B4" s="19" t="n"/>
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="19" t="n"/>
+      <c r="E4" s="19" t="n"/>
+      <c r="F4" s="19" t="n"/>
+      <c r="G4" s="19" t="n"/>
+      <c r="H4" s="19" t="n"/>
+      <c r="I4" s="20" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -5175,6 +5285,10 @@
           <t>BẢNG B5 - DANH SÁCH FILE TEST WHITE-BOX VÀ NỘI DUNG KIỂM THỬ</t>
         </is>
       </c>
+      <c r="B1" s="19" t="n"/>
+      <c r="C1" s="19" t="n"/>
+      <c r="D1" s="19" t="n"/>
+      <c r="E1" s="20" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -5189,6 +5303,10 @@
           <t>DANH SÁCH FILE KIỂM THỬ HỘP TRẮNG</t>
         </is>
       </c>
+      <c r="B4" s="19" t="n"/>
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="19" t="n"/>
+      <c r="E4" s="20" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
